--- a/data/raw/市场板块成交统计.xlsx
+++ b/data/raw/市场板块成交统计.xlsx
@@ -5,30 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuanhm\Documents\bse_dashboard\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuanhm\Documents\GitHub\bse_dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16166998-5797-4620-999D-3EA2D619972E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D50CB3-C6CB-4F33-858C-C55B272E2558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -623,7 +610,7 @@
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="5" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" customWidth="1"/>
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
@@ -633,7 +620,7 @@
     <col min="16" max="16" width="15.7109375" customWidth="1"/>
     <col min="17" max="17" width="16.7109375" customWidth="1"/>
     <col min="18" max="23" width="18.7109375" customWidth="1"/>
-    <col min="24" max="24" width="15.7109375" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" customWidth="1"/>
     <col min="25" max="26" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -802,79 +789,79 @@
         <v>13</v>
       </c>
       <c r="B3" s="3">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="C3" s="4">
-        <v>66760.083743880008</v>
+        <v>70405.767795330001</v>
       </c>
       <c r="D3" s="4">
-        <v>927228.47687608004</v>
+        <v>991848.64281908004</v>
       </c>
       <c r="E3" s="4">
-        <v>612.47783251266003</v>
+        <v>612.22406778547804</v>
       </c>
       <c r="F3" s="4">
-        <v>8506.6832740924765</v>
+        <v>8624.7708071224351</v>
       </c>
       <c r="G3" s="4">
-        <v>59310.300609140002</v>
+        <v>62718.147494379999</v>
       </c>
       <c r="H3" s="4">
-        <v>858214.04077315005</v>
+        <v>915982.49568230996</v>
       </c>
       <c r="I3" s="4">
-        <v>544.13119824899104</v>
+        <v>545.37519560330395</v>
       </c>
       <c r="J3" s="4">
-        <v>7873.5233098454128</v>
+        <v>7965.065179846174</v>
       </c>
       <c r="K3" s="4">
-        <v>26347.130916590002</v>
+        <v>27892.450834089999</v>
       </c>
       <c r="L3" s="4">
-        <v>768255.54097743996</v>
+        <v>824641.48772878002</v>
       </c>
       <c r="M3" s="4">
-        <v>241.71679739990799</v>
+        <v>242.54305073121702</v>
       </c>
       <c r="N3" s="4">
-        <v>7048.2159722700917</v>
+        <v>7170.795545467653</v>
       </c>
       <c r="O3" s="4">
-        <v>5776.4402661399999</v>
+        <v>6195.3891382100001</v>
       </c>
       <c r="P3" s="4">
-        <v>354238.75244802999</v>
+        <v>386781.96622348001</v>
       </c>
       <c r="Q3" s="4">
-        <v>52.994864826971998</v>
+        <v>53.872949027913002</v>
       </c>
       <c r="R3" s="4">
-        <v>3249.8968114498161</v>
+        <v>3363.3214454215649</v>
       </c>
       <c r="S3" s="4">
-        <v>958.35478174000002</v>
+        <v>1014.26838561</v>
       </c>
       <c r="T3" s="4">
-        <v>23654.126263000002</v>
+        <v>25092.194525179999</v>
       </c>
       <c r="U3" s="4">
-        <v>8.7922457040370006</v>
+        <v>8.8197250922610007</v>
       </c>
       <c r="V3" s="4">
-        <v>217.01033268807302</v>
+        <v>218.19299587112999</v>
       </c>
       <c r="W3" s="4">
-        <v>213960.70722050001</v>
+        <v>227472.98169544002</v>
       </c>
       <c r="X3" s="4">
-        <v>562290.86978780001</v>
+        <v>593506.08531618991</v>
       </c>
       <c r="Y3" s="4">
-        <v>1962.9422680779819</v>
+        <v>1978.025927786435</v>
       </c>
       <c r="Z3" s="4">
-        <v>5158.6318329155956</v>
+        <v>5160.9224810103478</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="15.9" x14ac:dyDescent="0.45">
